--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,49 +671,49 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI SW Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>BayOne Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>PR, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Senior GCP ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,15 +1221,155 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Data Engineer l</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PepperPointe Partnerships</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c95a1853e484041c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
+          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,15 +688,15 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,15 +723,15 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI SW Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BayOne Solutions</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, MySQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=000259e18029be16</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c48a092ef1e42df2</t>
+          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Senior GCP ML Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08b8b745d8fa7fac</t>
+          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior GCP ML Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,15 +1143,15 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineer l</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PepperPointe Partnerships</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Lexington, KY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer l</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PepperPointe Partnerships</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lexington, KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
+          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,42 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Bunton Real Estate Co.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3051d76e04b9f7d5</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior GCP ML Engineer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,287 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Software Test Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>GCP Support Associate</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>MI, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Buffalo, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Data Engineer l</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>PepperPointe Partnerships</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Lexington, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Docker, Airflow, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a16dfe0847dba18</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>NY, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Bunton Real Estate Co.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9911da7c780080ec</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,84 +916,84 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,58 +1003,583 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>Solutions Engineer II - Networking</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Test Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Peoria, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GCP Support Associate</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MI, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Buffalo, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>Dallas, TX, US USA</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D33" t="n">
         <v>10.4</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>Data Validation Engineer (ML)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>35.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Azure</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=0aa9d1342b93a57e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>AI &amp; Data Solution Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,50 +653,50 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,49 +741,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,164 +846,164 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,94 +1081,94 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,15 +1571,190 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,42 +793,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Software Test Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,42 +1283,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1755,6 +1755,41 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Test Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, Snowflake, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7de7c68f8d61272</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,42 +1283,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1755,41 +1755,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI &amp; Data Solution Architect</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Medallion Architecture, Google Cloud Platform, GCP</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e27010d95a9e3bd</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,42 +793,42 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,42 +1248,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,24 +1326,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1720,41 +1720,6 @@
         </is>
       </c>
       <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior GCP ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,94 +1221,94 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,15 +1318,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,24 +1676,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,227 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,59 +601,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
+          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,24 +696,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -723,32 +723,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>CrowdStrike Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
+          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior GCP ML Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,49 +1231,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404bcc6e4c24eef4</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1353,15 +1353,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,24 +1571,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f335fe8313e7021</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,262 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -596,12 +596,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eced97189d3f1514</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CrowdStrike Cloud Security Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,25 +758,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c455c9d7ebf2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CrowdStrike GenAI Security Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, API Gateway, ECS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90098a812a3f2e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2c542b1c6936ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CrowdStrike AI Security Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d17925590b6bc95</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c0bc93046858fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
         </is>
       </c>
     </row>
@@ -1687,6 +1687,41 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Airflow ML Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Cloud Data Architect-5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>22.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, Athena, S3, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=d6408ada685f1f82</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Java Developer-2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=58ab9ef429e9dd15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Java Developer-2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=52ca61e6deb7ad68</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,32 +653,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,50 +688,50 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>Hadoop Developer-6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>Hadoop Developer-6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,49 +986,49 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior SRE Cloud Enablement Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Acuity Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,15 +1038,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Selenium Automation tester-6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,49 +1091,49 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d1e820641acb1c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,50 +1143,50 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Databricks Data Engineer(Azure + Python)-6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>OIPA Engineer-7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,14 +1616,14 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Airflow ML Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,15 +1711,295 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior Engineer - .NET</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Engineer - Java [Hybrid]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Airflow ML Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-6</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OIPA Engineer-7</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)-6</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
+          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>OIPA Engineer-7</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
+          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
+          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Databricks Data Engineer(Azure + Python)-6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
+          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>OIPA Engineer-7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
+          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
+          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-6</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
+          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>OIPA Engineer-7</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Hadoop Developer-6</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
+          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>Hadoop Developer-6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,32 +933,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior SRE Cloud Enablement Engineer</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Acuity Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4536dd4ecaee73e9</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Selenium Automation tester-6</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d1e820641acb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Selenium Automation tester-6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=a7d1e820641acb1c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>CrowdStrike Security Trainee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior GCP ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-6</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>OIPA Engineer-7</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Okta IAM Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,15 +1423,15 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
+          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,24 +1466,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
+          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
+          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
+          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
+          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Databricks Data Engineer(Azure + Python)-6</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>OIPA Engineer-7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior GCP Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer - .NET</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,24 +1921,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Airflow ML Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,15 +1991,155 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Airflow ML Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>

--- a/results/job_matches_2026-03-29.xlsx
+++ b/results/job_matches_2026-03-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,42 +548,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=955ac0b1ad8a879b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Developer-2</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,59 +591,59 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58ab9ef429e9dd15</t>
+          <t>https://www.indeed.com/viewjob?jk=afb300209d5a9cc9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Java Developer-2</t>
+          <t>CrowdStrike Container Security Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ca61e6deb7ad68</t>
+          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>GCP ML Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,32 +653,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, RDS, Kafka, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, GCP, MLOps</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd16761f5f52ad01</t>
+          <t>https://www.indeed.com/viewjob?jk=ce062c1221d36aca</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCP ML Architect</t>
+          <t>Endpoint Privilege Management Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f760910209d307d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Endpoint Privilege Management Specialist</t>
+          <t>Hadoop Developer-6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e8cab942be0127b</t>
+          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3afabcdb51ae0d33</t>
+          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hadoop Developer-6</t>
+          <t>Integrations Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>The Cheesecake Factory</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Calabasas Hills, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=808ff57e896a509d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Integrations Analyst</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Cheesecake Factory</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Calabasas Hills, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba075cb0dad311d7</t>
+          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, ETL, ELT, dbt, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085882623e9376f9</t>
+          <t>https://www.indeed.com/viewjob?jk=20a8124f877384e7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>LLM Deployment Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,32 +898,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Hadoop, Spark, Scala, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fbda0b80cc8b17</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SAP AI Business Services Consultant</t>
+          <t>AI Agent Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,32 +933,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, Dask, MLOps, MLflow, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40c91983bc2eae41</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LLM Deployment Engineer</t>
+          <t>SAP Certified Associate – SAP Cloud</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, API Gateway, ECS, RDS, Hive</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc848e376ba98b</t>
+          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Agent Operations Engineer</t>
+          <t>GCP AI Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, PySpark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd5fe5ca4da283b</t>
+          <t>https://www.indeed.com/viewjob?jk=037a88873ec44a68</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAP Certified Associate – SAP Cloud</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff9128969c03a5d</t>
+          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer- Policy Configuration</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ec6455a3649dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Selenium Automation tester-6</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,49 +1126,49 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7d1e820641acb1c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6eea039facef1d5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CrowdStrike Container Security Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da369ed0415378f8</t>
+          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Policy Configuration</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,15 +1178,15 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e80b3d6f63774f05</t>
+          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CrowdStrike Security Trainee</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5acfaf4bd1f75434</t>
+          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GCP ML Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1de5b143abbaf230</t>
+          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Databricks Data Engineer(Azure + Python)-6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,14 +1301,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835a9e46d2da0aa</t>
+          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1318,15 +1318,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2e91ea7c7c3f142</t>
+          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c088d2367959ce00</t>
+          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,15 +1388,15 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f05354d748a5aeb</t>
+          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Okta IAM Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49485783185c2a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Kafka, NoSQL, CI/CD, Terraform, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99da7d209a64961d</t>
+          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, MLOps, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e369b21b51e562d</t>
+          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ff36ecb3e92993</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ded6a35597c773</t>
+          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - .NET</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,24 +1606,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
+          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
+          <t>Senior Engineer - Java [Hybrid]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-6</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c37b249c5a57dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0abc5e7ae8fc4129</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OIPA Engineer-7</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,24 +1711,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Oracle, SQL Server, MLOps, Jenkins, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c3d63dc6cec641</t>
+          <t>https://www.indeed.com/viewjob?jk=0a38818212ef4e3d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior GCP Kubernetes Engineer</t>
+          <t>Airflow ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1755,391 +1755,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96cd6cc30dd40084</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9155e920851da33</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=185eae839798cd18</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer - (Java, React, Data Lake, Microservices) - *HYBRID*</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa6f70357a9e424</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e8c6ea0f8c6d982</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Senior Engineer - .NET</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2741f8d01d2c064</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Engineer - Java [Hybrid]</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b05a12260b85b7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0902efec6021373c</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13aad62ce3d79441</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=91ef5be98f953dc8</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5061df3b805eed6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Airflow ML Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, ETL, Docker, Kubernetes, Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7d1c715f07cfc17f</t>
         </is>
